--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCAF9C7-4F66-48BD-9003-E5697C602695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDCBACA-BED6-466D-A28C-5B93381C106C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -178,57 +178,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -569,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -1566,7 +1516,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>10109011</v>
+        <v>1010902</v>
       </c>
       <c r="B91" s="1">
         <v>1010901</v>
@@ -1577,10 +1527,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>10109012</v>
+        <v>1010903</v>
       </c>
       <c r="B92" s="1">
-        <v>10109011</v>
+        <v>1010902</v>
       </c>
       <c r="C92" s="1">
         <v>1</v>
@@ -1588,10 +1538,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>1010902</v>
+        <v>1010904</v>
       </c>
       <c r="B93" s="1">
-        <v>1010901</v>
+        <v>1010903</v>
       </c>
       <c r="C93" s="1">
         <v>1</v>
@@ -1599,10 +1549,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>1010903</v>
-      </c>
-      <c r="B94" s="1">
-        <v>1010902</v>
+        <v>1010905</v>
+      </c>
+      <c r="B94" s="5">
+        <v>1010904</v>
       </c>
       <c r="C94" s="1">
         <v>1</v>
@@ -1610,10 +1560,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>1010904</v>
+        <v>905010202</v>
       </c>
       <c r="B95" s="1">
-        <v>1010903</v>
+        <v>905010101</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
@@ -1621,10 +1571,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>1010905</v>
-      </c>
-      <c r="B96" s="5">
-        <v>1010904</v>
+        <v>905010302</v>
+      </c>
+      <c r="B96" s="1">
+        <v>905010202</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
@@ -1632,10 +1582,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>1010906</v>
-      </c>
-      <c r="B97" s="5">
-        <v>1010905</v>
+        <v>905010403</v>
+      </c>
+      <c r="B97" s="1">
+        <v>905010302</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -1643,10 +1593,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>1010907</v>
-      </c>
-      <c r="B98" s="5">
-        <v>1010906</v>
+        <v>905010503</v>
+      </c>
+      <c r="B98" s="1">
+        <v>905010403</v>
       </c>
       <c r="C98" s="1">
         <v>1</v>
@@ -1654,10 +1604,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>1010908</v>
-      </c>
-      <c r="B99" s="5">
-        <v>1010907</v>
+        <v>905010604</v>
+      </c>
+      <c r="B99" s="1">
+        <v>905010503</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -1665,10 +1615,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>1010909</v>
-      </c>
-      <c r="B100" s="5">
-        <v>1010908</v>
+        <v>905010704</v>
+      </c>
+      <c r="B100" s="1">
+        <v>905010604</v>
       </c>
       <c r="C100" s="1">
         <v>1</v>
@@ -1676,10 +1626,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>1010910</v>
-      </c>
-      <c r="B101" s="5">
-        <v>1010909</v>
+        <v>905010805</v>
+      </c>
+      <c r="B101" s="1">
+        <v>905010704</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
@@ -1687,10 +1637,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>905010202</v>
+        <v>901010202</v>
       </c>
       <c r="B102" s="1">
-        <v>905010101</v>
+        <v>901010101</v>
       </c>
       <c r="C102" s="1">
         <v>1</v>
@@ -1698,10 +1648,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>905010302</v>
+        <v>901010302</v>
       </c>
       <c r="B103" s="1">
-        <v>905010202</v>
+        <v>901010202</v>
       </c>
       <c r="C103" s="1">
         <v>1</v>
@@ -1709,10 +1659,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>905010403</v>
+        <v>901010403</v>
       </c>
       <c r="B104" s="1">
-        <v>905010302</v>
+        <v>901010302</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -1720,10 +1670,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>905010503</v>
+        <v>901010503</v>
       </c>
       <c r="B105" s="1">
-        <v>905010403</v>
+        <v>901010403</v>
       </c>
       <c r="C105" s="1">
         <v>1</v>
@@ -1731,10 +1681,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>905010604</v>
+        <v>901010604</v>
       </c>
       <c r="B106" s="1">
-        <v>905010503</v>
+        <v>901010503</v>
       </c>
       <c r="C106" s="1">
         <v>1</v>
@@ -1742,10 +1692,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>905010704</v>
+        <v>901010704</v>
       </c>
       <c r="B107" s="1">
-        <v>905010604</v>
+        <v>901010604</v>
       </c>
       <c r="C107" s="1">
         <v>1</v>
@@ -1753,10 +1703,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>905010805</v>
+        <v>901010805</v>
       </c>
       <c r="B108" s="1">
-        <v>905010704</v>
+        <v>901010704</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -1764,10 +1714,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>901010202</v>
+        <v>902010202</v>
       </c>
       <c r="B109" s="1">
-        <v>901010101</v>
+        <v>902010101</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -1775,10 +1725,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>901010302</v>
+        <v>902010302</v>
       </c>
       <c r="B110" s="1">
-        <v>901010202</v>
+        <v>902010202</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -1786,10 +1736,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>901010403</v>
+        <v>902010403</v>
       </c>
       <c r="B111" s="1">
-        <v>901010302</v>
+        <v>902010302</v>
       </c>
       <c r="C111" s="1">
         <v>1</v>
@@ -1797,10 +1747,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>901010503</v>
+        <v>902010503</v>
       </c>
       <c r="B112" s="1">
-        <v>901010403</v>
+        <v>902010403</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
@@ -1808,10 +1758,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>901010604</v>
+        <v>902010604</v>
       </c>
       <c r="B113" s="1">
-        <v>901010503</v>
+        <v>902010503</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
@@ -1819,10 +1769,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>901010704</v>
+        <v>902010704</v>
       </c>
       <c r="B114" s="1">
-        <v>901010604</v>
+        <v>902010604</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
@@ -1830,10 +1780,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>901010805</v>
+        <v>902010805</v>
       </c>
       <c r="B115" s="1">
-        <v>901010704</v>
+        <v>902010704</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
@@ -1841,10 +1791,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>902010202</v>
+        <v>903010202</v>
       </c>
       <c r="B116" s="1">
-        <v>902010101</v>
+        <v>903010101</v>
       </c>
       <c r="C116" s="1">
         <v>1</v>
@@ -1852,10 +1802,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>902010302</v>
+        <v>903010302</v>
       </c>
       <c r="B117" s="1">
-        <v>902010202</v>
+        <v>903010202</v>
       </c>
       <c r="C117" s="1">
         <v>1</v>
@@ -1863,10 +1813,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>902010403</v>
+        <v>903010403</v>
       </c>
       <c r="B118" s="1">
-        <v>902010302</v>
+        <v>903010302</v>
       </c>
       <c r="C118" s="1">
         <v>1</v>
@@ -1874,10 +1824,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>902010503</v>
+        <v>903010503</v>
       </c>
       <c r="B119" s="1">
-        <v>902010403</v>
+        <v>903010403</v>
       </c>
       <c r="C119" s="1">
         <v>1</v>
@@ -1885,10 +1835,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>902010604</v>
+        <v>903010604</v>
       </c>
       <c r="B120" s="1">
-        <v>902010503</v>
+        <v>903010503</v>
       </c>
       <c r="C120" s="1">
         <v>1</v>
@@ -1896,10 +1846,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>902010704</v>
+        <v>903010704</v>
       </c>
       <c r="B121" s="1">
-        <v>902010604</v>
+        <v>903010604</v>
       </c>
       <c r="C121" s="1">
         <v>1</v>
@@ -1907,10 +1857,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>902010805</v>
+        <v>903010805</v>
       </c>
       <c r="B122" s="1">
-        <v>902010704</v>
+        <v>903010704</v>
       </c>
       <c r="C122" s="1">
         <v>1</v>
@@ -1918,10 +1868,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>903010202</v>
+        <v>900010202</v>
       </c>
       <c r="B123" s="1">
-        <v>903010101</v>
+        <v>900010101</v>
       </c>
       <c r="C123" s="1">
         <v>1</v>
@@ -1929,10 +1879,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>903010302</v>
+        <v>900010302</v>
       </c>
       <c r="B124" s="1">
-        <v>903010202</v>
+        <v>900010202</v>
       </c>
       <c r="C124" s="1">
         <v>1</v>
@@ -1940,10 +1890,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>903010403</v>
+        <v>900010403</v>
       </c>
       <c r="B125" s="1">
-        <v>903010302</v>
+        <v>900010302</v>
       </c>
       <c r="C125" s="1">
         <v>1</v>
@@ -1951,10 +1901,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>903010503</v>
+        <v>900010503</v>
       </c>
       <c r="B126" s="1">
-        <v>903010403</v>
+        <v>900010403</v>
       </c>
       <c r="C126" s="1">
         <v>1</v>
@@ -1962,10 +1912,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>903010604</v>
+        <v>900010604</v>
       </c>
       <c r="B127" s="1">
-        <v>903010503</v>
+        <v>900010503</v>
       </c>
       <c r="C127" s="1">
         <v>1</v>
@@ -1973,10 +1923,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>903010704</v>
+        <v>900010704</v>
       </c>
       <c r="B128" s="1">
-        <v>903010604</v>
+        <v>900010604</v>
       </c>
       <c r="C128" s="1">
         <v>1</v>
@@ -1984,397 +1934,12 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>903010805</v>
+        <v>900010805</v>
       </c>
       <c r="B129" s="1">
-        <v>903010704</v>
+        <v>900010704</v>
       </c>
       <c r="C129" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A130" s="1">
-        <v>900010202</v>
-      </c>
-      <c r="B130" s="1">
-        <v>900010101</v>
-      </c>
-      <c r="C130" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A131" s="1">
-        <v>900010302</v>
-      </c>
-      <c r="B131" s="1">
-        <v>900010202</v>
-      </c>
-      <c r="C131" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A132" s="1">
-        <v>900010403</v>
-      </c>
-      <c r="B132" s="1">
-        <v>900010302</v>
-      </c>
-      <c r="C132" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A133" s="1">
-        <v>900010503</v>
-      </c>
-      <c r="B133" s="1">
-        <v>900010403</v>
-      </c>
-      <c r="C133" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A134" s="1">
-        <v>900010604</v>
-      </c>
-      <c r="B134" s="1">
-        <v>900010503</v>
-      </c>
-      <c r="C134" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A135" s="1">
-        <v>900010704</v>
-      </c>
-      <c r="B135" s="1">
-        <v>900010604</v>
-      </c>
-      <c r="C135" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A136" s="1">
-        <v>900010805</v>
-      </c>
-      <c r="B136" s="1">
-        <v>900010704</v>
-      </c>
-      <c r="C136" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A137" s="1">
-        <v>900020202</v>
-      </c>
-      <c r="B137" s="1">
-        <v>900020101</v>
-      </c>
-      <c r="C137" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A138" s="1">
-        <v>900020302</v>
-      </c>
-      <c r="B138" s="1">
-        <v>900020202</v>
-      </c>
-      <c r="C138" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A139" s="1">
-        <v>900020403</v>
-      </c>
-      <c r="B139" s="1">
-        <v>900020302</v>
-      </c>
-      <c r="C139" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A140" s="1">
-        <v>900020503</v>
-      </c>
-      <c r="B140" s="1">
-        <v>900020403</v>
-      </c>
-      <c r="C140" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A141" s="1">
-        <v>900020604</v>
-      </c>
-      <c r="B141" s="1">
-        <v>900020503</v>
-      </c>
-      <c r="C141" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A142" s="1">
-        <v>900020704</v>
-      </c>
-      <c r="B142" s="1">
-        <v>900020604</v>
-      </c>
-      <c r="C142" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A143" s="1">
-        <v>900020805</v>
-      </c>
-      <c r="B143" s="1">
-        <v>900020704</v>
-      </c>
-      <c r="C143" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A144" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="B144" s="1">
-        <v>901020101</v>
-      </c>
-      <c r="C144" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A145" s="1">
-        <v>901020302</v>
-      </c>
-      <c r="B145" s="1">
-        <v>901020101</v>
-      </c>
-      <c r="C145" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A146" s="1">
-        <v>901020403</v>
-      </c>
-      <c r="B146" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="C146" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A147" s="1">
-        <v>901020503</v>
-      </c>
-      <c r="B147" s="1">
-        <v>901020302</v>
-      </c>
-      <c r="C147" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A148" s="1">
-        <v>901020604</v>
-      </c>
-      <c r="B148" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="C148" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A149" s="1">
-        <v>901020704</v>
-      </c>
-      <c r="B149" s="1">
-        <v>901020302</v>
-      </c>
-      <c r="C149" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A150" s="1">
-        <v>901020805</v>
-      </c>
-      <c r="B150" s="1">
-        <v>901020202</v>
-      </c>
-      <c r="C150" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A151" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="B151" s="1">
-        <v>902020101</v>
-      </c>
-      <c r="C151" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A152" s="1">
-        <v>902020302</v>
-      </c>
-      <c r="B152" s="1">
-        <v>902020101</v>
-      </c>
-      <c r="C152" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A153" s="1">
-        <v>902020403</v>
-      </c>
-      <c r="B153" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="C153" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A154" s="1">
-        <v>902020503</v>
-      </c>
-      <c r="B154" s="1">
-        <v>902020302</v>
-      </c>
-      <c r="C154" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A155" s="1">
-        <v>902020604</v>
-      </c>
-      <c r="B155" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="C155" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A156" s="1">
-        <v>902020704</v>
-      </c>
-      <c r="B156" s="1">
-        <v>902020302</v>
-      </c>
-      <c r="C156" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A157" s="1">
-        <v>902020805</v>
-      </c>
-      <c r="B157" s="1">
-        <v>902020202</v>
-      </c>
-      <c r="C157" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A158" s="1">
-        <v>903020202</v>
-      </c>
-      <c r="B158" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C158" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A159" s="1">
-        <v>903020302</v>
-      </c>
-      <c r="B159" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C159" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A160" s="1">
-        <v>903020403</v>
-      </c>
-      <c r="B160" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C160" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A161" s="1">
-        <v>903020503</v>
-      </c>
-      <c r="B161" s="1">
-        <v>903020302</v>
-      </c>
-      <c r="C161" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A162" s="1">
-        <v>903020604</v>
-      </c>
-      <c r="B162" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C162" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A163" s="1">
-        <v>903020704</v>
-      </c>
-      <c r="B163" s="1">
-        <v>903020302</v>
-      </c>
-      <c r="C163" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A164" s="1">
-        <v>903020805</v>
-      </c>
-      <c r="B164" s="1">
-        <v>903020101</v>
-      </c>
-      <c r="C164" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2386,21 +1951,6 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_front_v8【迷宫-能力词条-前置词条组】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDCBACA-BED6-466D-A28C-5B93381C106C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCAF9C7-4F66-48BD-9003-E5697C602695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D693F5A6-F9B8-466E-A083-AAC4F5D7E3BD}"/>
   </bookViews>
@@ -178,7 +178,57 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -519,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BC824-40D3-4285-8894-FF1F5862FC8E}">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -1516,7 +1566,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>1010902</v>
+        <v>10109011</v>
       </c>
       <c r="B91" s="1">
         <v>1010901</v>
@@ -1527,10 +1577,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>1010903</v>
+        <v>10109012</v>
       </c>
       <c r="B92" s="1">
-        <v>1010902</v>
+        <v>10109011</v>
       </c>
       <c r="C92" s="1">
         <v>1</v>
@@ -1538,10 +1588,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>1010904</v>
+        <v>1010902</v>
       </c>
       <c r="B93" s="1">
-        <v>1010903</v>
+        <v>1010901</v>
       </c>
       <c r="C93" s="1">
         <v>1</v>
@@ -1549,10 +1599,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>1010905</v>
-      </c>
-      <c r="B94" s="5">
-        <v>1010904</v>
+        <v>1010903</v>
+      </c>
+      <c r="B94" s="1">
+        <v>1010902</v>
       </c>
       <c r="C94" s="1">
         <v>1</v>
@@ -1560,10 +1610,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>905010202</v>
+        <v>1010904</v>
       </c>
       <c r="B95" s="1">
-        <v>905010101</v>
+        <v>1010903</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
@@ -1571,10 +1621,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>905010302</v>
-      </c>
-      <c r="B96" s="1">
-        <v>905010202</v>
+        <v>1010905</v>
+      </c>
+      <c r="B96" s="5">
+        <v>1010904</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
@@ -1582,10 +1632,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>905010403</v>
-      </c>
-      <c r="B97" s="1">
-        <v>905010302</v>
+        <v>1010906</v>
+      </c>
+      <c r="B97" s="5">
+        <v>1010905</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
@@ -1593,10 +1643,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>905010503</v>
-      </c>
-      <c r="B98" s="1">
-        <v>905010403</v>
+        <v>1010907</v>
+      </c>
+      <c r="B98" s="5">
+        <v>1010906</v>
       </c>
       <c r="C98" s="1">
         <v>1</v>
@@ -1604,10 +1654,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>905010604</v>
-      </c>
-      <c r="B99" s="1">
-        <v>905010503</v>
+        <v>1010908</v>
+      </c>
+      <c r="B99" s="5">
+        <v>1010907</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -1615,10 +1665,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>905010704</v>
-      </c>
-      <c r="B100" s="1">
-        <v>905010604</v>
+        <v>1010909</v>
+      </c>
+      <c r="B100" s="5">
+        <v>1010908</v>
       </c>
       <c r="C100" s="1">
         <v>1</v>
@@ -1626,10 +1676,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>905010805</v>
-      </c>
-      <c r="B101" s="1">
-        <v>905010704</v>
+        <v>1010910</v>
+      </c>
+      <c r="B101" s="5">
+        <v>1010909</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
@@ -1637,10 +1687,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>901010202</v>
+        <v>905010202</v>
       </c>
       <c r="B102" s="1">
-        <v>901010101</v>
+        <v>905010101</v>
       </c>
       <c r="C102" s="1">
         <v>1</v>
@@ -1648,10 +1698,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>901010302</v>
+        <v>905010302</v>
       </c>
       <c r="B103" s="1">
-        <v>901010202</v>
+        <v>905010202</v>
       </c>
       <c r="C103" s="1">
         <v>1</v>
@@ -1659,10 +1709,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>901010403</v>
+        <v>905010403</v>
       </c>
       <c r="B104" s="1">
-        <v>901010302</v>
+        <v>905010302</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
@@ -1670,10 +1720,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>901010503</v>
+        <v>905010503</v>
       </c>
       <c r="B105" s="1">
-        <v>901010403</v>
+        <v>905010403</v>
       </c>
       <c r="C105" s="1">
         <v>1</v>
@@ -1681,10 +1731,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>901010604</v>
+        <v>905010604</v>
       </c>
       <c r="B106" s="1">
-        <v>901010503</v>
+        <v>905010503</v>
       </c>
       <c r="C106" s="1">
         <v>1</v>
@@ -1692,10 +1742,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>901010704</v>
+        <v>905010704</v>
       </c>
       <c r="B107" s="1">
-        <v>901010604</v>
+        <v>905010604</v>
       </c>
       <c r="C107" s="1">
         <v>1</v>
@@ -1703,10 +1753,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>901010805</v>
+        <v>905010805</v>
       </c>
       <c r="B108" s="1">
-        <v>901010704</v>
+        <v>905010704</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
@@ -1714,10 +1764,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>902010202</v>
+        <v>901010202</v>
       </c>
       <c r="B109" s="1">
-        <v>902010101</v>
+        <v>901010101</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
@@ -1725,10 +1775,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>902010302</v>
+        <v>901010302</v>
       </c>
       <c r="B110" s="1">
-        <v>902010202</v>
+        <v>901010202</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
@@ -1736,10 +1786,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>902010403</v>
+        <v>901010403</v>
       </c>
       <c r="B111" s="1">
-        <v>902010302</v>
+        <v>901010302</v>
       </c>
       <c r="C111" s="1">
         <v>1</v>
@@ -1747,10 +1797,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>902010503</v>
+        <v>901010503</v>
       </c>
       <c r="B112" s="1">
-        <v>902010403</v>
+        <v>901010403</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
@@ -1758,10 +1808,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>902010604</v>
+        <v>901010604</v>
       </c>
       <c r="B113" s="1">
-        <v>902010503</v>
+        <v>901010503</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
@@ -1769,10 +1819,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>902010704</v>
+        <v>901010704</v>
       </c>
       <c r="B114" s="1">
-        <v>902010604</v>
+        <v>901010604</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
@@ -1780,10 +1830,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>902010805</v>
+        <v>901010805</v>
       </c>
       <c r="B115" s="1">
-        <v>902010704</v>
+        <v>901010704</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
@@ -1791,10 +1841,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>903010202</v>
+        <v>902010202</v>
       </c>
       <c r="B116" s="1">
-        <v>903010101</v>
+        <v>902010101</v>
       </c>
       <c r="C116" s="1">
         <v>1</v>
@@ -1802,10 +1852,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>903010302</v>
+        <v>902010302</v>
       </c>
       <c r="B117" s="1">
-        <v>903010202</v>
+        <v>902010202</v>
       </c>
       <c r="C117" s="1">
         <v>1</v>
@@ -1813,10 +1863,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>903010403</v>
+        <v>902010403</v>
       </c>
       <c r="B118" s="1">
-        <v>903010302</v>
+        <v>902010302</v>
       </c>
       <c r="C118" s="1">
         <v>1</v>
@@ -1824,10 +1874,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>903010503</v>
+        <v>902010503</v>
       </c>
       <c r="B119" s="1">
-        <v>903010403</v>
+        <v>902010403</v>
       </c>
       <c r="C119" s="1">
         <v>1</v>
@@ -1835,10 +1885,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>903010604</v>
+        <v>902010604</v>
       </c>
       <c r="B120" s="1">
-        <v>903010503</v>
+        <v>902010503</v>
       </c>
       <c r="C120" s="1">
         <v>1</v>
@@ -1846,10 +1896,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>903010704</v>
+        <v>902010704</v>
       </c>
       <c r="B121" s="1">
-        <v>903010604</v>
+        <v>902010604</v>
       </c>
       <c r="C121" s="1">
         <v>1</v>
@@ -1857,10 +1907,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>903010805</v>
+        <v>902010805</v>
       </c>
       <c r="B122" s="1">
-        <v>903010704</v>
+        <v>902010704</v>
       </c>
       <c r="C122" s="1">
         <v>1</v>
@@ -1868,10 +1918,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>900010202</v>
+        <v>903010202</v>
       </c>
       <c r="B123" s="1">
-        <v>900010101</v>
+        <v>903010101</v>
       </c>
       <c r="C123" s="1">
         <v>1</v>
@@ -1879,10 +1929,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>900010302</v>
+        <v>903010302</v>
       </c>
       <c r="B124" s="1">
-        <v>900010202</v>
+        <v>903010202</v>
       </c>
       <c r="C124" s="1">
         <v>1</v>
@@ -1890,10 +1940,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>900010403</v>
+        <v>903010403</v>
       </c>
       <c r="B125" s="1">
-        <v>900010302</v>
+        <v>903010302</v>
       </c>
       <c r="C125" s="1">
         <v>1</v>
@@ -1901,10 +1951,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>900010503</v>
+        <v>903010503</v>
       </c>
       <c r="B126" s="1">
-        <v>900010403</v>
+        <v>903010403</v>
       </c>
       <c r="C126" s="1">
         <v>1</v>
@@ -1912,10 +1962,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>900010604</v>
+        <v>903010604</v>
       </c>
       <c r="B127" s="1">
-        <v>900010503</v>
+        <v>903010503</v>
       </c>
       <c r="C127" s="1">
         <v>1</v>
@@ -1923,10 +1973,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>900010704</v>
+        <v>903010704</v>
       </c>
       <c r="B128" s="1">
-        <v>900010604</v>
+        <v>903010604</v>
       </c>
       <c r="C128" s="1">
         <v>1</v>
@@ -1934,12 +1984,397 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
+        <v>903010805</v>
+      </c>
+      <c r="B129" s="1">
+        <v>903010704</v>
+      </c>
+      <c r="C129" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A130" s="1">
+        <v>900010202</v>
+      </c>
+      <c r="B130" s="1">
+        <v>900010101</v>
+      </c>
+      <c r="C130" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A131" s="1">
+        <v>900010302</v>
+      </c>
+      <c r="B131" s="1">
+        <v>900010202</v>
+      </c>
+      <c r="C131" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A132" s="1">
+        <v>900010403</v>
+      </c>
+      <c r="B132" s="1">
+        <v>900010302</v>
+      </c>
+      <c r="C132" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A133" s="1">
+        <v>900010503</v>
+      </c>
+      <c r="B133" s="1">
+        <v>900010403</v>
+      </c>
+      <c r="C133" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A134" s="1">
+        <v>900010604</v>
+      </c>
+      <c r="B134" s="1">
+        <v>900010503</v>
+      </c>
+      <c r="C134" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A135" s="1">
+        <v>900010704</v>
+      </c>
+      <c r="B135" s="1">
+        <v>900010604</v>
+      </c>
+      <c r="C135" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A136" s="1">
         <v>900010805</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B136" s="1">
         <v>900010704</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A137" s="1">
+        <v>900020202</v>
+      </c>
+      <c r="B137" s="1">
+        <v>900020101</v>
+      </c>
+      <c r="C137" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A138" s="1">
+        <v>900020302</v>
+      </c>
+      <c r="B138" s="1">
+        <v>900020202</v>
+      </c>
+      <c r="C138" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A139" s="1">
+        <v>900020403</v>
+      </c>
+      <c r="B139" s="1">
+        <v>900020302</v>
+      </c>
+      <c r="C139" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A140" s="1">
+        <v>900020503</v>
+      </c>
+      <c r="B140" s="1">
+        <v>900020403</v>
+      </c>
+      <c r="C140" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A141" s="1">
+        <v>900020604</v>
+      </c>
+      <c r="B141" s="1">
+        <v>900020503</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A142" s="1">
+        <v>900020704</v>
+      </c>
+      <c r="B142" s="1">
+        <v>900020604</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A143" s="1">
+        <v>900020805</v>
+      </c>
+      <c r="B143" s="1">
+        <v>900020704</v>
+      </c>
+      <c r="C143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A144" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="B144" s="1">
+        <v>901020101</v>
+      </c>
+      <c r="C144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A145" s="1">
+        <v>901020302</v>
+      </c>
+      <c r="B145" s="1">
+        <v>901020101</v>
+      </c>
+      <c r="C145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A146" s="1">
+        <v>901020403</v>
+      </c>
+      <c r="B146" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="C146" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A147" s="1">
+        <v>901020503</v>
+      </c>
+      <c r="B147" s="1">
+        <v>901020302</v>
+      </c>
+      <c r="C147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A148" s="1">
+        <v>901020604</v>
+      </c>
+      <c r="B148" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A149" s="1">
+        <v>901020704</v>
+      </c>
+      <c r="B149" s="1">
+        <v>901020302</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A150" s="1">
+        <v>901020805</v>
+      </c>
+      <c r="B150" s="1">
+        <v>901020202</v>
+      </c>
+      <c r="C150" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A151" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="B151" s="1">
+        <v>902020101</v>
+      </c>
+      <c r="C151" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A152" s="1">
+        <v>902020302</v>
+      </c>
+      <c r="B152" s="1">
+        <v>902020101</v>
+      </c>
+      <c r="C152" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A153" s="1">
+        <v>902020403</v>
+      </c>
+      <c r="B153" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="C153" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A154" s="1">
+        <v>902020503</v>
+      </c>
+      <c r="B154" s="1">
+        <v>902020302</v>
+      </c>
+      <c r="C154" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A155" s="1">
+        <v>902020604</v>
+      </c>
+      <c r="B155" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A156" s="1">
+        <v>902020704</v>
+      </c>
+      <c r="B156" s="1">
+        <v>902020302</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A157" s="1">
+        <v>902020805</v>
+      </c>
+      <c r="B157" s="1">
+        <v>902020202</v>
+      </c>
+      <c r="C157" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A158" s="1">
+        <v>903020202</v>
+      </c>
+      <c r="B158" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A159" s="1">
+        <v>903020302</v>
+      </c>
+      <c r="B159" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A160" s="1">
+        <v>903020403</v>
+      </c>
+      <c r="B160" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A161" s="1">
+        <v>903020503</v>
+      </c>
+      <c r="B161" s="1">
+        <v>903020302</v>
+      </c>
+      <c r="C161" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A162" s="1">
+        <v>903020604</v>
+      </c>
+      <c r="B162" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A163" s="1">
+        <v>903020704</v>
+      </c>
+      <c r="B163" s="1">
+        <v>903020302</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A164" s="1">
+        <v>903020805</v>
+      </c>
+      <c r="B164" s="1">
+        <v>903020101</v>
+      </c>
+      <c r="C164" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1951,6 +2386,21 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B139">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B141">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B142">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
